--- a/data/UngHoThi.xlsx
+++ b/data/UngHoThi.xlsx
@@ -1,193 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30412"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyProjectMakeMoney\SupportFriend\tusmeplus-supportfriend\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC79D4CD-B9F8-4DE3-827A-1C3088BE863D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-28920" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
-  <si>
-    <t>STT</t>
-  </si>
-  <si>
-    <t>Tên</t>
-  </si>
-  <si>
-    <t>18200</t>
-  </si>
-  <si>
-    <t>Đặng Lâm Thúy Nhuy</t>
-  </si>
-  <si>
-    <t>Đặng Võ Bảo Trân</t>
-  </si>
-  <si>
-    <t>Đào Thị Bé Ngọc</t>
-  </si>
-  <si>
-    <t>Hồng Thị Hà</t>
-  </si>
-  <si>
-    <t>Huỳnh Lục Thái Lam</t>
-  </si>
-  <si>
-    <t>Huỳnh Tấn Tú</t>
-  </si>
-  <si>
-    <t>Huỳnh Thanh Thiện</t>
-  </si>
-  <si>
-    <t>Huỳnh Thị Hậu</t>
-  </si>
-  <si>
-    <t>Huỳnh Thị Thúy Ngân</t>
-  </si>
-  <si>
-    <t>Lê Mỹ Phiên</t>
-  </si>
-  <si>
-    <t>Lê Thị Kim Ngọc</t>
-  </si>
-  <si>
-    <t>Lê Thị Thúy Nhi</t>
-  </si>
-  <si>
-    <t>Lê Xuân Diễm</t>
-  </si>
-  <si>
-    <t>Lý Minh Tuệ</t>
-  </si>
-  <si>
-    <t>Mai Thị Kim Son</t>
-  </si>
-  <si>
-    <t>Ngô Thị Ngọc Nhung</t>
-  </si>
-  <si>
-    <t>Nguyễn Cửu Minh Duyên</t>
-  </si>
-  <si>
-    <t>Nguyễn Hoài Duy</t>
-  </si>
-  <si>
-    <t>Nguyễn Minh Trung</t>
-  </si>
-  <si>
-    <t>Đã chuyển trả</t>
-  </si>
-  <si>
-    <t>Nguyễn Nhật Mỹ</t>
-  </si>
-  <si>
-    <t>Nguyễn Thái An</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Duy</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Phú</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Quân</t>
-  </si>
-  <si>
-    <t>Nguyễn Thanh Sơn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Ánh Thúy</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Ngọc Sang</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Ngọc Thái</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Như Quỳnh</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Thanh Thủy</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Thanh Tú</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Thúy Hậu</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn Lập</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn Thuận</t>
-  </si>
-  <si>
-    <t>Phạm Thị Phương Trinh</t>
-  </si>
-  <si>
-    <t>Phạm Thị Thúy</t>
-  </si>
-  <si>
-    <t>Phan Nguyễn Thành Trung</t>
-  </si>
-  <si>
-    <t>Qua Bình Thu Thảo</t>
-  </si>
-  <si>
-    <t>Ti</t>
-  </si>
-  <si>
-    <t>Trần Duy Khang</t>
-  </si>
-  <si>
-    <t>Trần Thị Diệu</t>
-  </si>
-  <si>
-    <t>Trần Thị Kim Diệu</t>
-  </si>
-  <si>
-    <t>Trần Thị Thanh Trúc</t>
-  </si>
-  <si>
-    <t>TRAN THI THANH TUYEN</t>
-  </si>
-  <si>
-    <t>Trương Đình Thọ</t>
-  </si>
-  <si>
-    <t>Trương Duy Khánh</t>
-  </si>
-  <si>
-    <t>Ung Duy Linh</t>
-  </si>
-  <si>
-    <t>Võ Minh Quốc</t>
-  </si>
-  <si>
-    <t>Võ Minh Tân</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -215,21 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -308,6 +150,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -342,6 +185,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -376,20 +220,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -511,561 +351,599 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>STT</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Tên</v>
+      </c>
+      <c r="C1" t="str">
+        <v>18200</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
+      <c r="B2" t="str">
+        <v>Đặng Lâm Thúy Nhuy</v>
       </c>
       <c r="C2">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
+      <c r="B3" t="str">
+        <v>Đặng Võ Bảo Trân</v>
       </c>
       <c r="C3">
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>5</v>
+      <c r="B4" t="str">
+        <v>Đào Thị Bé Ngọc</v>
       </c>
       <c r="C4">
         <v>1000</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>6</v>
+      <c r="B5" t="str">
+        <v>Hồng Thị Hà</v>
       </c>
       <c r="C5">
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B6" t="str">
+        <v>Huỳnh Lục Thái Lam</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Đã chuyển trả</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>8</v>
+      <c r="B7" t="str">
+        <v>Huỳnh Tấn Tú</v>
       </c>
       <c r="C7">
         <v>300</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>9</v>
+      <c r="B8" t="str">
+        <v>Huỳnh Thanh Thiện</v>
       </c>
       <c r="C8">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>10</v>
+      <c r="B9" t="str">
+        <v>Huỳnh Thị Hậu</v>
       </c>
       <c r="C9">
         <v>400</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>11</v>
+      <c r="B10" t="str">
+        <v>Huỳnh Thị Thúy Ngân</v>
       </c>
       <c r="C10">
         <v>300</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>12</v>
+      <c r="B11" t="str">
+        <v>Lê Mỹ Phiên</v>
       </c>
       <c r="C11">
         <v>200</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>13</v>
+      <c r="B12" t="str">
+        <v>Lê Thị Kim Ngọc</v>
       </c>
       <c r="C12">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>14</v>
+      <c r="B13" t="str">
+        <v>Lê Thị Thúy Nhi</v>
       </c>
       <c r="C13">
         <v>500</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>15</v>
+      <c r="B14" t="str">
+        <v>Lê Xuân Diễm</v>
       </c>
       <c r="C14">
         <v>1080</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>16</v>
+      <c r="B15" t="str">
+        <v>Lý Minh Tuệ</v>
       </c>
       <c r="C15">
         <v>500</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>17</v>
+      <c r="B16" t="str">
+        <v>Mai Thị Kim Son</v>
       </c>
       <c r="C16">
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
-        <v>18</v>
+      <c r="B17" t="str">
+        <v>Ngô Thị Ngọc Nhung</v>
       </c>
       <c r="C17">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B18" t="str">
+        <v>Nguyễn Cửu Minh Duyên</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Đã chuyển trả</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
-        <v>20</v>
+      <c r="B19" t="str">
+        <v>Nguyễn Hoài Duy</v>
       </c>
       <c r="C19">
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B20" t="str">
+        <v>Nguyễn Minh Trung</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Đã chuyển trả</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B21" t="str">
+        <v>Nguyễn Nhật Mỹ</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Đã chuyển trả</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B22" t="str">
+        <v>Nguyễn Thái An</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Đã chuyển trả</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
-        <v>25</v>
+      <c r="B23" t="str">
+        <v>Nguyễn Thành Duy</v>
       </c>
       <c r="C23">
         <v>500</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>26</v>
+      <c r="B24" t="str">
+        <v>Nguyễn Thành Phú</v>
       </c>
       <c r="C24">
         <v>400</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
-        <v>27</v>
+      <c r="B25" t="str">
+        <v>Nguyễn Thành Quân</v>
       </c>
       <c r="C25">
         <v>200</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
-        <v>28</v>
+      <c r="B26" t="str">
+        <v>Nguyễn Thanh Sơn</v>
       </c>
       <c r="C26">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
-        <v>29</v>
+      <c r="B27" t="str">
+        <v>Nguyễn Thị Ánh Thúy</v>
       </c>
       <c r="C27">
         <v>800</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
-        <v>30</v>
-      </c>
-      <c r="C28">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B28" t="str">
+        <v>Nguyễn Thị Ngọc Sang</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Đã chuyển trả</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
-        <v>31</v>
+      <c r="B29" t="str">
+        <v>Nguyễn Thị Ngọc Thái</v>
       </c>
       <c r="C29">
         <v>300</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
-        <v>32</v>
+      <c r="B30" t="str">
+        <v>Nguyễn Thị Như Quỳnh</v>
       </c>
       <c r="C30">
         <v>300</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
-        <v>33</v>
+      <c r="B31" t="str">
+        <v>Nguyễn Thị Thanh Thủy</v>
       </c>
       <c r="C31">
         <v>500</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
-        <v>34</v>
+      <c r="B32" t="str">
+        <v>Nguyễn Thị Thanh Tú</v>
       </c>
       <c r="C32">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
-        <v>35</v>
+      <c r="B33" t="str">
+        <v>Nguyễn Thị Thúy Hậu</v>
       </c>
       <c r="C33">
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
-        <v>36</v>
+      <c r="B34" t="str">
+        <v>Nguyễn Văn Lập</v>
       </c>
       <c r="C34">
         <v>1000</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
-        <v>37</v>
+      <c r="B35" t="str">
+        <v>Nguyễn Văn Thuận</v>
       </c>
       <c r="C35">
         <v>300</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
-        <v>38</v>
+      <c r="B36" t="str">
+        <v>Phạm Thị Phương Trinh</v>
       </c>
       <c r="C36">
         <v>300</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
-        <v>39</v>
+      <c r="B37" t="str">
+        <v>Phạm Thị Thúy</v>
       </c>
       <c r="C37">
         <v>200</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
-        <v>40</v>
+      <c r="B38" t="str">
+        <v>Phan Nguyễn Thành Trung</v>
       </c>
       <c r="C38">
         <v>500</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
-        <v>41</v>
+      <c r="B39" t="str">
+        <v>Qua Bình Thu Thảo</v>
       </c>
       <c r="C39">
         <v>120</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
-        <v>42</v>
+      <c r="B40" t="str">
+        <v>Ti</v>
       </c>
       <c r="C40">
         <v>500</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
-        <v>43</v>
+      <c r="B41" t="str">
+        <v>Trần Duy Khang</v>
       </c>
       <c r="C41">
         <v>500</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
-        <v>44</v>
+      <c r="B42" t="str">
+        <v>Trần Thị Diệu</v>
       </c>
       <c r="C42">
         <v>300</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
-        <v>45</v>
-      </c>
-      <c r="C43" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B43" t="str">
+        <v>Trần Thị Kim Diệu</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Đã chuyển trả</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
-        <v>46</v>
-      </c>
-      <c r="C44" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B44" t="str">
+        <v>Trần Thị Thanh Trúc</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Đã chuyển trả</v>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
-        <v>47</v>
-      </c>
-      <c r="C45" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B45" t="str">
+        <v>TRAN THI THANH TUYEN</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Đã chuyển trả</v>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
-        <v>48</v>
+      <c r="B46" t="str">
+        <v>Trương Đình Thọ</v>
       </c>
       <c r="C46">
         <v>500</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" t="s">
-        <v>49</v>
+      <c r="B47" t="str">
+        <v>Trương Duy Khánh</v>
       </c>
       <c r="C47">
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48">
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
-        <v>50</v>
+      <c r="B48" t="str">
+        <v>Ung Duy Linh</v>
       </c>
       <c r="C48">
         <v>200</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49">
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" t="s">
-        <v>51</v>
+      <c r="B49" t="str">
+        <v>Võ Minh Quốc</v>
       </c>
       <c r="C49">
         <v>100</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" t="s">
-        <v>52</v>
+      <c r="B50" t="str">
+        <v>Võ Minh Tân</v>
       </c>
       <c r="C50">
         <v>200</v>
@@ -1073,5 +951,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C50"/>
+  </ignoredErrors>
 </worksheet>
 </file>